--- a/budget/budget-planning-sheet-2026.xlsx
+++ b/budget/budget-planning-sheet-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/treedoug/Documents/Proposals/2026-Microrobots_Proposal_NSF_Cammy/white_papers/v5_2026-06-23_for_NSF/budget/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/treedoug/Documents/Proposals/2026-Microrobots_NSF/budget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224B14D3-32CD-C24E-86BB-75F3FABCB6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4A282B-77E2-414D-BB45-61DF63731E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33600" yWindow="600" windowWidth="33600" windowHeight="37200" xr2:uid="{A315EF21-8A52-4BF1-B80C-1C391945B20A}"/>
+    <workbookView xWindow="33600" yWindow="600" windowWidth="33600" windowHeight="37200" activeTab="4" xr2:uid="{A315EF21-8A52-4BF1-B80C-1C391945B20A}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget p.1" sheetId="3" r:id="rId1"/>
@@ -460,7 +460,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="102">
   <si>
     <t>Period 1</t>
   </si>
@@ -915,6 +915,9 @@
   </si>
   <si>
     <t>Rich</t>
+  </si>
+  <si>
+    <t>From my 2025-2026 Salary</t>
   </si>
 </sst>
 </file>
@@ -4293,15 +4296,14 @@
         <v>45930</v>
       </c>
       <c r="B8" s="57">
-        <f>B7*1.03</f>
-        <v>131048.96000000001</v>
+        <v>133988</v>
       </c>
       <c r="C8" s="58">
         <f t="shared" si="0"/>
-        <v>16374.567552</v>
+        <v>16741.800599999999</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="57"/>
@@ -4314,13 +4316,15 @@
       </c>
       <c r="B9" s="57">
         <f t="shared" ref="B9:B13" si="1">B8*1.03</f>
-        <v>134980.42880000002</v>
+        <v>138007.64000000001</v>
       </c>
       <c r="C9" s="58">
         <f t="shared" si="0"/>
-        <v>16865.804578560004</v>
-      </c>
-      <c r="D9" s="57"/>
+        <v>17244.054618000002</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>69</v>
+      </c>
       <c r="E9" s="56"/>
       <c r="F9" s="57"/>
       <c r="G9" s="57"/>
@@ -4332,11 +4336,11 @@
       </c>
       <c r="B10" s="57">
         <f t="shared" si="1"/>
-        <v>139029.84166400004</v>
+        <v>142147.86920000002</v>
       </c>
       <c r="C10" s="58">
         <f t="shared" si="0"/>
-        <v>17371.778715916804</v>
+        <v>17761.376256540003</v>
       </c>
       <c r="D10" s="57"/>
       <c r="E10" s="56"/>
@@ -4350,11 +4354,11 @@
       </c>
       <c r="B11" s="57">
         <f t="shared" si="1"/>
-        <v>143200.73691392003</v>
+        <v>146412.30527600003</v>
       </c>
       <c r="C11" s="58">
         <f t="shared" si="0"/>
-        <v>17892.932077394307</v>
+        <v>18294.217544236202</v>
       </c>
       <c r="D11" s="57"/>
       <c r="E11" s="56"/>
@@ -4368,11 +4372,11 @@
       </c>
       <c r="B12" s="57">
         <f t="shared" si="1"/>
-        <v>147496.75902133764</v>
+        <v>150804.67443428002</v>
       </c>
       <c r="C12" s="58">
         <f t="shared" si="0"/>
-        <v>18429.72003971614</v>
+        <v>18843.04407056329</v>
       </c>
       <c r="D12" s="57"/>
       <c r="E12" s="56"/>
@@ -4386,11 +4390,11 @@
       </c>
       <c r="B13" s="57">
         <f t="shared" si="1"/>
-        <v>151921.66179197776</v>
+        <v>155328.81466730844</v>
       </c>
       <c r="C13" s="58">
         <f t="shared" si="0"/>
-        <v>18982.61164090762</v>
+        <v>19408.335392680186</v>
       </c>
       <c r="D13" s="57"/>
       <c r="E13" s="56"/>
